--- a/docs/import_templates/technoflow_import_template_leads.xlsx
+++ b/docs/import_templates/technoflow_import_template_leads.xlsx
@@ -434,27 +434,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="36" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="36" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,85 +466,90 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Lead category *</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Company name *</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CRM lead code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Contact person</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Designation</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Emirate / city</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Service / product interest</t>
-        </is>
-      </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Product interest</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Estimated value</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Sales Engineer</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Date received</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Next follow-up</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Reference (your own unique ID)</t>
         </is>
@@ -555,51 +561,52 @@
           <t>Chiller replacement - Tower A</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Example Contracting LLC</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Mr. Sample Person</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>buyer@example-contracting.example</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>150000</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>LEAD-001</t>
         </is>
@@ -611,12 +618,12 @@
           <t>Pump room upgrade</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Sample Facilities Management</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -624,30 +631,31 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>64000</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Contacted</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
         <is>
           <t>LEAD-002</t>
         </is>
@@ -664,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -745,7 +753,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Company name</t>
+          <t>Lead category</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -753,31 +761,35 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Job in Hand, Tender or Purchase Enquiry.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Job In Hand, Purchase Enquiry, Tender</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>CRM lead code</t>
+          <t>Company name</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Only to update an existing lead (LD-…).</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Contact person</t>
+          <t>CRM lead code</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -785,13 +797,17 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Only to update an existing lead (LD-…).</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Designation</t>
+          <t>Contact person</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -805,7 +821,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Designation</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -819,7 +835,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -833,7 +849,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Emirate / city</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -847,7 +863,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Emirate / city</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -856,16 +872,12 @@
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Direct Visit, Referral, Partnership, Website, Phone Enquiry, Email Enquiry, Exhibition, Tender</t>
-        </is>
-      </c>
+      <c r="D14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Service / product interest</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -874,12 +886,16 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Direct Visit, Referral, Partnership, Website, Phone Enquiry, Email Enquiry, Exhibition, Tender</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Estimated value</t>
+          <t>Product interest</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -893,7 +909,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Estimated value</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -902,16 +918,12 @@
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>High, Low, Medium</t>
-        </is>
-      </c>
+      <c r="D17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Stage</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -919,21 +931,17 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>An open lead stage, e.g. New, Contacted, Qualified. Empty = the first stage. Import completed deals as Opportunities.</t>
-        </is>
-      </c>
+      <c r="C18" s="3" t="inlineStr"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>New, Contacted, Qualification, Qualified, Proposal in Preparation, Proposal Submitted, Negotiation</t>
+          <t>High, Low, Medium</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Sales Engineer</t>
+          <t>Stage</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -943,15 +951,19 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Employee's CRM username, work email or employee ID. Empty = you, if you are a Sales Engineer or Coordinator; otherwise required.</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr"/>
+          <t>An open lead stage, e.g. New, Contacted, Qualified. Empty = the first stage. Import completed deals as Opportunities.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>New, Contacted, Qualification, Qualified, Proposal in Preparation, Proposal Submitted, Negotiation</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Date received</t>
+          <t>Sales Engineer</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -961,19 +973,15 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Kept as the lead's real date (not the upload date). Empty = today.</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-15 or 15/03/2026</t>
-        </is>
-      </c>
+          <t>Employee's CRM username, work email or employee ID. Empty = you, if you are a Sales Engineer or Coordinator; otherwise required.</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Next follow-up</t>
+          <t>Date received</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -981,7 +989,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Kept as the lead's real date (not the upload date). Empty = today.</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
           <t>2026-03-15 or 15/03/2026</t>
@@ -991,7 +1003,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Next follow-up</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1000,25 +1012,43 @@
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-15 or 15/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t>Reference (your own unique ID)</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Optional but recommended. The same reference uploaded again is recognised as the same record.</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
